--- a/Sheets/IT MID.xlsx
+++ b/Sheets/IT MID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\Code\python_IT_SEU\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06FF41D-1DE8-4B7E-86AC-9BEAFA0DED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95700CBF-A1A8-402F-8706-A339AEEAE2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="112">
   <si>
     <t>Mid term</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Final Course Project</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.19921875" bestFit="1" customWidth="1"/>
@@ -812,7 +815,7 @@
     <col min="7" max="7" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -832,7 +835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2025002937</v>
       </c>
@@ -844,7 +847,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2025002750</v>
       </c>
@@ -856,7 +859,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2025002445</v>
       </c>
@@ -868,7 +871,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2025001214</v>
       </c>
@@ -880,7 +883,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2025000248</v>
       </c>
@@ -892,7 +895,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2025000977</v>
       </c>
@@ -904,7 +907,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2025001348</v>
       </c>
@@ -916,7 +919,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2025001358</v>
       </c>
@@ -928,7 +931,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2025002092</v>
       </c>
@@ -940,7 +943,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2025002457</v>
       </c>
@@ -952,7 +955,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2025001209</v>
       </c>
@@ -964,7 +967,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2025001676</v>
       </c>
@@ -975,8 +978,14 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>16901</v>
+      </c>
+      <c r="K13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2025002010</v>
       </c>
@@ -988,7 +997,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2025001768</v>
       </c>
@@ -1000,7 +1009,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2025001457</v>
       </c>

--- a/Sheets/IT MID.xlsx
+++ b/Sheets/IT MID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\Code\python_IT_SEU\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Student_Grades\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95700CBF-A1A8-402F-8706-A339AEEAE2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EAB4DE-95D6-4714-A8CD-BC9E37DB7D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>Mid term</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t>Final Course Project</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -803,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.19921875" bestFit="1" customWidth="1"/>
@@ -815,7 +812,7 @@
     <col min="7" max="7" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -835,7 +832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>2025002937</v>
       </c>
@@ -847,7 +844,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2025002750</v>
       </c>
@@ -859,7 +856,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2025002445</v>
       </c>
@@ -871,7 +868,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2025001214</v>
       </c>
@@ -883,7 +880,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2025000248</v>
       </c>
@@ -895,7 +892,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2025000977</v>
       </c>
@@ -907,7 +904,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2025001348</v>
       </c>
@@ -919,7 +916,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2025001358</v>
       </c>
@@ -931,7 +928,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2025002092</v>
       </c>
@@ -943,7 +940,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2025002457</v>
       </c>
@@ -955,7 +952,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2025001209</v>
       </c>
@@ -967,7 +964,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2025001676</v>
       </c>
@@ -978,14 +975,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="J13">
-        <v>16901</v>
-      </c>
-      <c r="K13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2025002010</v>
       </c>
@@ -997,7 +988,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2025001768</v>
       </c>
@@ -1009,7 +1000,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2025001457</v>
       </c>
